--- a/data/pokemon_master_test.xlsx
+++ b/data/pokemon_master_test.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1013C1D-0D66-426F-91F5-1566551E0804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="456" windowWidth="17280" windowHeight="12504" xr2:uid="{ABC960E6-03C1-49DF-964F-B08A81FF98E0}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9420" xr2:uid="{ABC960E6-03C1-49DF-964F-B08A81FF98E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/pokemon_master_test.xlsx
+++ b/data/pokemon_master_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\闇鍋\PCM資料\ポケモンクイズ\pokemon-image-quiz\pokemon-image-quiz\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1013C1D-0D66-426F-91F5-1566551E0804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7388F6-02EA-43A0-B7F7-429E2E3DCE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9420" xr2:uid="{ABC960E6-03C1-49DF-964F-B08A81FF98E0}"/>
+    <workbookView xWindow="-20340" yWindow="4740" windowWidth="17280" windowHeight="9420" xr2:uid="{ABC960E6-03C1-49DF-964F-B08A81FF98E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>id</t>
     <phoneticPr fontId="1"/>
@@ -74,30 +74,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0052a</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0052c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0052b</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0646a</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>646b</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>646c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>0772</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -180,10 +156,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>images/0052-Normal.png</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>images/0052-Alola.png</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -200,7 +172,59 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>images/0646-Normal.png</t>
+    <t>region</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tags</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kanto</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alola</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>galar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unova</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>images/0052.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>images/0646.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0052</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0052-Alola</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0052-Galar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0646-White</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0646-Black</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0646</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -588,16 +612,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662611C-8EB7-4DA7-9B24-0B7B46770313}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1"/>
+    <col min="1" max="1" width="10.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.09765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="106.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,165 +638,201 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
       <c r="E11" t="b">
         <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
